--- a/AAII_Financials/Quarterly/OMVKY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OMVKY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="92">
   <si>
     <t>OMVKY</t>
   </si>
@@ -656,177 +656,181 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -869,86 +873,89 @@
       <c r="P8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R8" s="3">
         <v>16068000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>18555600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>16096300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>17222400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>14471700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>9165500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7687400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6801900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4943100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3836100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3423300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5192700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>7090800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>7287500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>7099600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6463100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>7854500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>6210300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>6265200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>5464700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>5504500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>5212800</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>5780500</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>6191100</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>6346800</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>6161300</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -991,86 +998,89 @@
       <c r="P9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R9" s="3">
         <v>12383000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>12835500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>11628500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>10985500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>9568300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>6578800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>5091100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4397000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3634500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2510700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2211300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3708000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4687200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4695400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4537400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4302700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>5203600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>4239900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>4662100</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>3530100</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>3775500</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>3518600</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>4149100</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>4238900</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>6463000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>5864400</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1113,86 +1123,89 @@
       <c r="P10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R10" s="3">
         <v>3685000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>5720100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4467700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>6237000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>4903400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2586700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2596300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2404800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1308600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1325400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1212000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1484700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2403700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2592100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2562200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2160300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2650900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1970400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1603100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1934700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1729000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1694200</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1631400</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1952300</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>-116200</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>297000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1279,86 +1293,89 @@
       <c r="P12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R12" s="3">
         <v>117400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>60500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>84900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>10900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>164800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>48500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>47600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>40200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>43900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>674600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>90500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>129800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>85200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>46500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>83500</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>55000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>71000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>27700</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>58200</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>40600</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>107700</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>39300</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>65100</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>35900</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>83300</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>77500</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1479,8 +1496,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1523,21 +1543,21 @@
       <c r="P14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>6500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-171900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1102200</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1550,11 +1570,11 @@
       <c r="Y14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>10</v>
+      <c r="Z14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>10</v>
@@ -1571,38 +1591,41 @@
       <c r="AF14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AG14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH14" s="3">
         <v>-158500</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>165000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>-68100</v>
       </c>
-      <c r="AJ14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK14" s="3">
+      <c r="AK14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL14" s="3">
         <v>-3400</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>-2200</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>1362100</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>-153700</v>
       </c>
-      <c r="AO14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AP14" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AQ14" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1645,86 +1668,89 @@
       <c r="P15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R15" s="3">
         <v>914900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>680800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>182800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>646300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>2002300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>721500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>654900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>649600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>342100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>986000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>536700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>690500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>728500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>719100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>677600</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>656700</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>553600</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>495100</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>516100</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>486400</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>511600</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>538600</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>518400</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>509400</v>
       </c>
-      <c r="AO15" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AP15" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AQ15" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,8 +1790,9 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1808,86 +1835,89 @@
       <c r="P17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R17" s="3">
         <v>14136300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>14924500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>12480500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>15105000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>12857400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>8184400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6549000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5756600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3494900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4510700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3330500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5054200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6229300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>6264600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5986700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5652000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>6430200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5483700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>5738100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>4596200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>4899700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>4581100</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>6672500</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>5163400</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>6659000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>6087400</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1930,86 +1960,89 @@
       <c r="P18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R18" s="3">
         <v>1931700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3631200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3615800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2117400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1614200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>981100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1138400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1045300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1448200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-674600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>92700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>138500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>861500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1022900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1112900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>811000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1424200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>726600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>527000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>868500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>604800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>631700</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>-892000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>1027700</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>-312200</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>74000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,8 +2085,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2096,86 +2130,89 @@
       <c r="P20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R20" s="3">
         <v>33200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>61600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>489600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>293800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>139800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>218600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>219000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>212700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>84800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>57100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>52400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-51300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>131900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>144500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>227000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>161500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>88700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>154000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>176800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>90000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>25800</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>225500</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>113300</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>149200</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>118600</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>166700</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2218,86 +2255,89 @@
       <c r="P21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R21" s="3">
         <v>2967300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>4417900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>4634200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3069500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3876700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1947000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2046200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1926600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2091500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>816800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>738500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>862900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1752300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1906100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2063400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1644800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2102000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1385600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1233100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1452700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1227500</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1405900</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>-194100</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1677400</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1205500</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>1295900</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2340,86 +2380,89 @@
       <c r="P22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R22" s="3">
         <v>118500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>111300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>120800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>103400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>90000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>105500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>80400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>81500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>70800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>73700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>68700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>81800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>85200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>95500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>90600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>89700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>82800</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>77500</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>94400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>70300</v>
       </c>
-      <c r="AK22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AL22" s="3">
+      <c r="AL22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM22" s="3">
         <v>80800</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>69600</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>68400</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>74000</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>78600</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2462,86 +2505,89 @@
       <c r="P23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R23" s="3">
         <v>1846400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3581400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3984600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2307900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1664100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1094100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1277000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1176500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1462200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-691200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>76400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>5500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>908200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1071900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1249300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>882800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1430100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>803000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>609400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>888300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>630600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>776400</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-848200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>1108500</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>-267600</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>162000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2584,86 +2630,89 @@
       <c r="P24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R24" s="3">
         <v>1351300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2112800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1251300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1376400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>930200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>572900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>422100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>293100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-478800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-216900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>14200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>79600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>373600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>416500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>475300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>289500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>492100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>366600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>306300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>305200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>159300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>166100</v>
-      </c>
-      <c r="AM24" s="3">
-        <v>193000</v>
       </c>
       <c r="AN24" s="3">
         <v>193000</v>
       </c>
       <c r="AO24" s="3">
+        <v>193000</v>
+      </c>
+      <c r="AP24" s="3">
         <v>120900</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,8 +2833,11 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2828,86 +2880,89 @@
       <c r="P26" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R26" s="3">
         <v>495100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1468700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2733300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>931400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>733900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>521200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>854900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>883400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1940900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-474300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>62200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-74200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>534700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>655400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>774100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>593300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>938000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>436400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>303000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>583000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>471200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>610400</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-1041200</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>915500</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>-388500</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>152600</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2950,86 +3005,89 @@
       <c r="P27" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R27" s="3">
         <v>341100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>900200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2118500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>594100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>583200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>300500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>658100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>691900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1875100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-505500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>26200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-173500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>414400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>520600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>638800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>423500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>719200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>244800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>222900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>445800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>348900</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>491400</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-1153400</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>798900</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>-442500</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>57500</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3194,8 +3255,8 @@
       <c r="P29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,8 +3583,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3560,86 +3630,89 @@
       <c r="P32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R32" s="3">
         <v>-33200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-61600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-489600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-293800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-139800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-218600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-219000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-212700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-84800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-57100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-52400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>51300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-131900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-144500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-227000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-161500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-88700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-154000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-176800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-90000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-25800</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-225500</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-113300</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-149200</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-118600</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-166700</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3682,86 +3755,89 @@
       <c r="P33" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R33" s="3">
         <v>341100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>900200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2118500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>594100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>583200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>300500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>658100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>691900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1875100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-505500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>26200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-173500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>414400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>520600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>638800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>423500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>719200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>244800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>222900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>445800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>348900</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>491400</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-1153400</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>798900</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>-442500</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>57500</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,8 +3958,11 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3926,213 +4005,219 @@
       <c r="P35" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R35" s="3">
         <v>341100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>900200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2118500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>594100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>583200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>300500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>658100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>691900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1875100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-505500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>26200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-173500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>414400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>520600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>638800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>423500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>719200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>244800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>222900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>445800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>348900</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>491400</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-1153400</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>798900</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>-442500</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>57500</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,1106 +4305,1134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3433100</v>
+      </c>
+      <c r="E41" s="3">
         <v>4042400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5961000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5217600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6178500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6142500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6400200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6462200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5673400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8450700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7648900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8238800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6828600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10278100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8960500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8222000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7118400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6550400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5474700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4373300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3271300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3625800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2846600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>7608800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6360000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3020700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3421700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3867300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4342100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4382900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4762400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3780200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3213800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4718100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>4456500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>5209400</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>4715700</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>3504000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>2428600</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>2051800</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1590300</v>
+      </c>
+      <c r="E42" s="3">
         <v>1972800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1020300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1459600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1327100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1230000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>879000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1270400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1471100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1933300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1528700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2363500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2328600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2192500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>4351800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>8071700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>8400100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>8005200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>5580900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>6690800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>9531500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>3779200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>3010200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>3291200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>5491600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>6987300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>3643500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>2736600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>3435100</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>2978500</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>3225800</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>4229900</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>2617600</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1327500</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1279100</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>1220700</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>905400</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>821300</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>1461400</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>1007100</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2706500</v>
+      </c>
+      <c r="E43" s="3">
         <v>2804100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2411600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2390000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2293600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2482700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3319200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3074900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3180100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3680000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4100800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3286400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3037100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4332900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4783700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6224800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5761500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5860500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5014000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3793900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4157900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4349400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3343300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1941900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1843600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2862500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3564100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3807300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3585700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>4357800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>4056200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3196500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2945900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3542100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2825200</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>2287700</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>2318000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>2921700</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>2924000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>3400500</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2985300</v>
+      </c>
+      <c r="E44" s="3">
         <v>2533100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2303600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2750200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2456800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2420000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4075000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4278400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4103700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4099700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3900700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4236900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4423600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4377400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5354100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5751500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>5589600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4256600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3414900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3245800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2706400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2507500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2345900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1541300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1538200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1572000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2153900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2370400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1909300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2075400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1858300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1845300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1639300</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1486700</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1686400</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1729000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1495600</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1647100</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1952000</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>2046000</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1209900</v>
+      </c>
+      <c r="E45" s="3">
         <v>1379000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>13891000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12994300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>13616000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>14071600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1940200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3417400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3196200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3336900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3838800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1079600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2438900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2999800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1806500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1022300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>805200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>768200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>674300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>525500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>431700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>538500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>534600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>273000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>293500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>370900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>347900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>286600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>294100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>330200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>312300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>418700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>424900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>362300</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>297300</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>269300</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>286100</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>280500</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>232400</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>367400</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>11925100</v>
+      </c>
+      <c r="E46" s="3">
         <v>12731500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>25656900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>24811700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>25872000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>26346700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16703600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>18503200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>17624600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>21500700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>21116400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>19205100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>19056800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>24180800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>25256600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>29292400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>27674700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>25440900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>20158800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>18629300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>20098800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>14800400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>12080500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>14656200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>15526900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>14813500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>13131000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>13068200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>13566200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>14124700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>14214900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>13470600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>10841700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>11436800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>10544500</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>10716100</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>9720900</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>9174500</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>8998400</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>8872800</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>15485000</v>
+      </c>
+      <c r="E47" s="3">
         <v>15409900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>6307400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>7436300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>7463300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>7556200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>7070100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>9039700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>8932800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>8726900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>8031400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>9185000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>9433400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>9563200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>10292900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>12286500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>11576300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>11807000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>11509900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>13968500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>13733900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>13026100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>11737400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>7767600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>8480700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>8646600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>8831500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>9770500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>6566700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>6554000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>6707000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>5998800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>5680000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>5236400</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>5466300</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>4431900</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>4404900</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>4145800</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>4468700</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>4164700</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>18658700</v>
+      </c>
+      <c r="E48" s="3">
         <v>18348900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>18456000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>18314000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>17862600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>16565100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>21147100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>22432500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21307200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21557900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>22196300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>21475400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>22336200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>21075600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>21395500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>20763500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>20747900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>20447600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>20130700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>19727700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>19286300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>19232300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>19153100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>14920900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>16464000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>16726900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>19237700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>20358100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>19369400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>19616500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>17879500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>15679200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>15670700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>14865800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>15319700</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>15457700</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>15748300</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>16063500</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>17152900</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>17763300</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1225900</v>
+      </c>
+      <c r="E49" s="3">
         <v>1237200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>955700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1312900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1323500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1225700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1438000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2288600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2073300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2054200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1329700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2315800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2355900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2812900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2780100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2888700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2820400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2798600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3426800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3611900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3541100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3695600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3434000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3190500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4212000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4215300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4859900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>5203800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4843200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>5048000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3923700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3202100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3188600</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>2882300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>2971000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1852400</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>1867000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>1934300</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>2010700</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>2851200</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>325600</v>
+      </c>
+      <c r="E52" s="3">
         <v>319400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>693900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>265200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>216100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>184800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>899700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>235300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>223900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>225500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>401200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>113300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>119000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>132600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3256300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3287500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3149000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3214200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3096200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3285600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3253400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4170600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2737900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2099700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2086900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1795600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1074000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>977500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>905800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>958200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>996000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1256000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1408700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1115600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1126500</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>935700</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1169100</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>3635200</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>5062600</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>2902800</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>49083700</v>
+      </c>
+      <c r="E54" s="3">
         <v>49625300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>54406500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>53404900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>54001200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>53049100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>50536300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>53789900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>51417600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>55303700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>55999800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>53561600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>54568800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>59086300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>62981500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>68518500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>65968200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>63708300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>58322400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>59223000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>59913500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>54925000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>49142900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>42634900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>46770600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>46197900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>47134200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>49378100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>45251400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>46301300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>43721200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>39606700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>36789600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>35536800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>35428000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>33393800</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>32910200</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>34953400</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>37693400</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>36554800</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3241200</v>
+      </c>
+      <c r="E57" s="3">
         <v>3389800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3091500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3358000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3208500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2970200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3854400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3841200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3832600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4082400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4371600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4369200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4121200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4477400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5824900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6514500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5991100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6072700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5268700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4034100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4424600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4777900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4292800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2667400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2607300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3769100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>4850600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>4789700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>4173900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>5197500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>5205900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>4101400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>3877000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>3910000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>3659900</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>3268400</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>3028300</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>3460200</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>4379500</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>4035600</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1684000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1696100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1662600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>504500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>975900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1019200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1486700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1236900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1097200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1255800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1268900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1642700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1522900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1683000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1742300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1111000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2053200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1191500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1383300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1852300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1045300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1936100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1689600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>855200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>916400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>613100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>943300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1768900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1664600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1934300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>997200</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>965800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1001400</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1902800</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1012000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>274900</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>218800</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>190700</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>305200</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>721900</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4817800</v>
+      </c>
+      <c r="E59" s="3">
         <v>4719200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7297200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8242400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>8156200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8705100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3278800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5093700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4839800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5877700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4458900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5114300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5109200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7136000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7940400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11723400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>10918000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>11148700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>8175200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>10021600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>11731100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5604200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4606000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5440700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>6826900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>8336700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>5174000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4881600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>5518500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>5219000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>5247300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>6182600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>4643400</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3090900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2986700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2753400</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>2555900</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>2606400</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>3211500</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>3006100</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9742900</v>
+      </c>
+      <c r="E60" s="3">
         <v>9805100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12956400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12104900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>12340600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>12694600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9792900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10171800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9769600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11215900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11569600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11126200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10753300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>13296400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>15507500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>19348900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>18962300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>18412800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>14827200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>15908000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>17201000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>12318300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>10588400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>8963300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>10350600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>12718900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>10967800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>11440200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>11357000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>12350800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>11450500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>11249900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>9521900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>8903700</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>7658700</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>6296600</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>5802900</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>6257300</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>7896200</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>7763600</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7452300</v>
+      </c>
+      <c r="E61" s="3">
         <v>7539500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7726900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7708600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7881400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7308700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8252400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9092100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8247100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8621200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8821700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8440900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>8885400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>9507800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>9648300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>9987800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>10084500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>10854900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>10382400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>10311300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>10897400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>10944000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>10215400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>9427200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>9955600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6896700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7957100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>8107000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>6550200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>6260900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5806900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5052900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>5035400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>5017900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>5375500</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>5134200</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>5244200</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>5276700</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>5869100</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>5379600</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5962500</v>
+      </c>
+      <c r="E62" s="3">
         <v>5744300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5674500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5525000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5270700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4930800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4852500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5370300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5155900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5206600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5363100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4663400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5316600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4952200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>8332500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>9227000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>8847300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>9078000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>9266900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>9469200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>9649000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>9182400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8491900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>7635800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>8515600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>8213500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>8523300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>9412800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>8512400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>8335100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>8315800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>6928000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>6508900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>6244300</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>6311200</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>5978000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>6342600</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>7216600</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>7582800</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>6944300</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>24808600</v>
+      </c>
+      <c r="E66" s="3">
         <v>24639700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>27911200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>26942400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>27122700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>26526200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>25050200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>26881600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>25274800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>27110800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>27958400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>26534700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>27278400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>30055400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>41770900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>46714300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>45687100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>45607700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>41513400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>42509600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>44194800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>39133300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>35438600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>29841700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>32870200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>32113100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>31943800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>33628400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>30806400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>31501900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>29637600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>26852700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>24489800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>23702500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>22843700</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>20852200</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>20777000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>22206400</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>24881300</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>23502000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>16707400</v>
+      </c>
+      <c r="E72" s="3">
         <v>17890000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>16469400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>16281800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>15722800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>15872200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>15037800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>15848800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>15053000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>16529300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>16397700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>15536600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>15520700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>16823100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>18378400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>18769600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>17224600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>15043000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>13671600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>12888300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>11960700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>12032600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>10195400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>9106500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>11379300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>11564700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>12445800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>12920000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>11727500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>12038600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>11306200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>10196600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>9765600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>9846900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>9714200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>9680500</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>9272100</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>9885900</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>9820100</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>10059600</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>20407900</v>
+      </c>
+      <c r="E76" s="3">
         <v>20665300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>19174600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>19033200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>19355300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>19136400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>18498800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>18939300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>18404600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20289100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20159200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19489800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19427900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>20837700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>21210500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>21804200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>20281100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>18100500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>16809000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>16713500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>15718700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>15791700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>13704300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>12793200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>13900400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>14084700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>15190300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>15749700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>14445000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>14799400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>14083600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>12754000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>12299800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>11834200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>12584200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>12541600</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>12133200</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>12746900</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>12812100</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>13052800</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,135 +8688,141 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8670,86 +8865,89 @@
       <c r="P81" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R81" s="3">
         <v>341100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>900200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2118500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>594100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>583200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>300500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>658100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>691900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1875100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-505500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>26200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-173500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>414400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>520600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>638800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>423500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>719200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>244800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>222900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>445800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>348900</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>491400</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-1153400</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>798900</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>-442500</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>57500</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>528500</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F83" s="3">
+        <v>534400</v>
+      </c>
+      <c r="E83" s="3">
+        <v>625800</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G83" s="3">
         <v>710500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>670700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>670000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>446600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>710200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>656100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>696400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>416800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>702100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>660700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>662100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1002400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>725100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>528800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>658300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>2122700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>747400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>688800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>668700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>558500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1434400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>593500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>775600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>758800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>738700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>723500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>672300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>589100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>505100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>529200</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>494100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>596900</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>548700</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>584600</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>500400</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>1533000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>1055300</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1502300</v>
+      </c>
+      <c r="E89" s="3">
         <v>894700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1973700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1283600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1271900</v>
       </c>
-      <c r="H89" s="3">
-        <v>1466700</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="I89" s="3">
+        <v>1467800</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K89" s="3">
         <v>1584900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1266500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1966800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1207000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1804600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>246700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2918300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1592700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3438800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>503800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2910700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3017100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1731700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1652600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1125700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>677200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>822000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>592400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1225100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1145200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1316900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1334000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1035900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1318900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1075500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1353800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1181400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>832500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>888600</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1110800</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1036700</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>718400</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>764200</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-823700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1071100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1194100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1091200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1133300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1013800</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="J91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K91" s="3">
         <v>-988200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-841100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-879300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1046800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-911300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-896300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-932200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-910000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-735000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-651000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-647000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-758000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-579000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-657000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-570300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-562500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-402700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-462500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-637100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-706300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-665200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-578800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-619600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-671900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-547200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-1866600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-473200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-571100</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-356800</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-373600</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-478000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-2844100</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-505900</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-862600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3366800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-921700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1228400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>138600</v>
       </c>
-      <c r="H94" s="3">
-        <v>-1124100</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="I94" s="3">
+        <v>-1125200</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K94" s="3">
         <v>-1315000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-832500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-884700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1110900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-265700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-859200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1069100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1040000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-967200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>1115300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1258900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-499800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-641800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-118500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-688800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4438400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-440100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-472400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-699300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-744800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3178800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-488200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1184200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-886000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-495100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1777700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-590700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-2453800</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-352300</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>379200</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>445400</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-206600</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-483600</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,130 +10455,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E96" s="3">
+      <c r="D96" s="3">
+        <v>1639400</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F96" s="3">
         <v>18800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>75100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1823800</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K96" s="3">
         <v>36800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>1782900</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="M96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N96" s="3">
+      <c r="N96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O96" s="3">
         <v>34900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>1819900</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>624700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-303700</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-91100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-35500</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
         <v>0</v>
       </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-451800</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-240000</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>115600</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-908200</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>85200</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-760900</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>59500</v>
       </c>
-      <c r="AL96" s="3">
-        <v>0</v>
-      </c>
       <c r="AM96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-653000</v>
       </c>
-      <c r="AN96" s="3">
-        <v>0</v>
-      </c>
       <c r="AO96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-99800</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1188200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-124500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>304100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1652000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1987100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>7600</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K100" s="3">
         <v>291100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3150100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-87400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-952800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-117500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2938900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-115200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-13300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1305500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1039100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-527700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1433200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-66800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1888500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>203100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-687200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1201900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>3212700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-661100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-640900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1214000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-818800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-275100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>288600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-39900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1066200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-232800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>886400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-31400</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-682200</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-142500</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>191300</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>219500</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-44600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-5400</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F101" s="3">
+      <c r="F101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G101" s="3">
         <v>-8900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-6600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-4200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-7600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-8700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-18200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>4900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>4200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-71100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-18800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>5400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>3300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-68600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-10800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-4300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-2100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-9500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-24900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-41500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-15200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-6100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>5900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-10800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>2400</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-13300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-5500</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-7700</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-7900</v>
-      </c>
-      <c r="AL101" s="3">
-        <v>-11200</v>
       </c>
       <c r="AM101" s="3">
         <v>-11200</v>
       </c>
       <c r="AN101" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="AO101" s="3">
         <v>-16800</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-39900</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-572400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2594300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1347900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1600400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-621300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>344800</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>552100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2717200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>995800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-863300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1417200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3559000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1725300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>520600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1171500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>583200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1055500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1073300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1018700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-356500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>630600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-4453400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1558900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>3333800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-176700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-255700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-654100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>32900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-434200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>723900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>527200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1495500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>350300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-742800</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>493700</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>796600</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>1322800</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>663200</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>496500</v>
       </c>
     </row>
